--- a/creativos-lomito-bakery/ebook/entregables/02-Bono-Calculadora-de-precios.xlsx
+++ b/creativos-lomito-bakery/ebook/entregables/02-Bono-Calculadora-de-precios.xlsx
@@ -77,7 +77,7 @@
     <t xml:space="preserve">CALCULADORA DE PRECIOS</t>
   </si>
   <si>
-    <t xml:space="preserve">Pastelería Canina que Vende · Lomito Bakery · Bono 2 de 5</t>
+    <t xml:space="preserve">Pastelería Canina que Vende · Lomito Bakery · Bono 1 de 5</t>
   </si>
   <si>
     <t xml:space="preserve">CÓMO SE USA</t>
